--- a/DH角色卡/半自动/DH1E角色卡Lite v2.11.xlsx
+++ b/DH角色卡/半自动/DH1E角色卡Lite v2.11.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="11630" tabRatio="500"/>
+    <workbookView windowWidth="11950" windowHeight="11630" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="人物" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">灵能大全!$B$2:$B$134</definedName>
-    <definedName name="预言">灵能大全!$C$64:$I$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">灵能大全!$B$2:$B$136</definedName>
+    <definedName name="预言">灵能大全!$C$65:$I$74</definedName>
     <definedName name="次级灵能" localSheetId="4">灵能大全!$C$3:$I$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="778">
   <si>
     <t>玩家</t>
   </si>
@@ -1311,6 +1311,17 @@
   </si>
   <si>
     <t>在此灵能的持续期间，灵能者不会留下任何他曾经来过的痕迹或证据，即使录像或录音等技术设备也无法记录。当然，这并不意味着灵能者当前的存在是无法被看到或被检测到的，而警报与陷阱也会被照常触发。</t>
+  </si>
+  <si>
+    <t>害兽语说</t>
+  </si>
+  <si>
+    <t>灵能者以意念延伸感知，借由附近生物的眼耳去看、与听。施展成功后，灵能者可以看见、听见五十米范围内任一目标所看到、听到的一切。灵能者必须先能察觉到某个生物的存在，然后才能对该目标施展灵能。维持这项灵能期间，灵能者每回合只能进行一个部分动作，因其注意力正被借来的耳目所分散。灵能者可以通过目标生物进行基于感知的检定，具体由游戏主持人裁定，检定使用目标生物的感知属性及其拥有的相关感知技能。
+这项灵能无法让灵能者借由目标所不具备的感官去感知。例如，目标没有眼睛则无法视物。同样，灵能者也无法使用目标拥有的特殊感官，例如声呐。
+注意：这项灵能不会赋予灵能者对其目标生物的控制权。目标生物将照常行动，并且可能游走出灵能的有效范围，此时灵能将自动终止。目标甚至有可能出于敌意或饥饿而攻击灵能者本人！灵能者可以使用其他灵能（如兽性主宰）来控制目标生物。</t>
+  </si>
+  <si>
+    <t>每超出阈值 5 点，灵能的有效距离增加 10 米。</t>
   </si>
   <si>
     <t>焚血咒</t>
@@ -1848,6 +1859,14 @@
   </si>
   <si>
     <t>你发射出一道带有单一命令的灵能波动，范围内所有人（不分敌我）都必须进行一次与你的意志对抗。你只需要掷一次骰子来对抗所有受到影响的人。任何输掉对抗的人都必须如同中了强迫行动灵能（见黑暗异端第 198 页）那样听从你的行动。你对范围内所发送的命令仅有一条。</t>
+  </si>
+  <si>
+    <t>野兽盟友</t>
+  </si>
+  <si>
+    <t>灵能者试图彻底支配一头野兽，使其留下铭印（imprint），成为自己的忠实盟友。这项灵能仅可作用于具有野兽特性、承伤少于 20 点，且智力属性至少为 05 的生物，游戏主持人可以酌情增设其他限制。
+施展灵能时，灵能者须与目标进行意志检定对抗。若灵能者获胜，野兽会将灵能者视为族群领袖，或同类中的支配者。野兽仍然依本能行动，但会紧伴灵能者左右，并遵从灵能者的传心指令。这项效果是永久性的。然而，若灵能者下达的命令会迫使野兽伤害自己（如步入火中、跳下悬崖等），灵能者必须通过一次艰巨难度（-20）的意志检定。检定成功，野兽遵从指令；反之，野兽将挣脱精神控制。灵能者可支配的野兽数量不得超过其灵能等级。
+如果灵能者未能支配该野兽，或野兽挣脱了控制，目标野兽便会扑向灵能者，狂怒地发起进攻，绝不逃跑或退缩。如果灵能者试图再次对该野兽使用这项灵能，目标野兽的意志检定获得 +10 加值。</t>
   </si>
   <si>
     <t>血肉面具</t>
@@ -7951,8 +7970,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="灵能表" displayName="灵能表" ref="B2:I135" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B2:I135" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="灵能表" displayName="灵能表" ref="B2:I137" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B2:I137" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="8">
     <tableColumn id="1" name="灵能名称"/>
     <tableColumn id="2" name="灵能类别" dataDxfId="0"/>
@@ -17414,12 +17433,12 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A41:AA58 A39:S39 L7:M7 A36:S36" numberStoredAsText="1"/>
-    <ignoredError sqref="A36 T35:AA35 Z2:Z3 G7:H7 T40:AA40 AD64:AY64 AZ71:BQ98 K7 Y4:Z4 H40:S40 K4:N4 A95:E98 A74:E93 A73:F73 A71:A72 A94:F94 A38:F38 T29:AA33 A15:BQ21 A8:BQ10 A6:O6 J4 A110:AY132" numberStoredAsText="1" formula="1"/>
-    <ignoredError sqref="I7:J7 A37:S37 A35:S35 R4:X4 A40:G40 I40:S40 O4:P4 K4:M4 F95:S98 F74:S93 G73:S73 B71:S72 G94:S94 G38:S38 A38:E38 A29:S33 A22:BQ22 A15:C16 E15:R16 A17:R17 A18:C18 E18:R18 A19:R21 T15:BQ21 E14:R14 A11:BQ11 M9:BQ10 K9:K10 I9:I10 E10:F10 A10:C10 A9:F9 A8:BQ8 P6:BQ6 I6:M6 A6:E6 A5:BQ5 A4:I4 A133:BQ159 AZ110:BQ132 A110:AC132 AB37:BQ40 AA2:BQ4 AC64:AC69 AZ54:BQ63 A99:AC99 AB71:AC98 O7:BQ7 A7 X3:Y3 C3:V3 A3 Y2 A2:W2 A1:BQ1 A70:AC70 A34:M34 T14:BQ14 A13:A14 A12:H12" numberStoredAsText="1" formula="1" formulaRange="1"/>
-    <ignoredError sqref="T35:AA35 AD54:AY63 AZ99:BQ99" formula="1"/>
-    <ignoredError sqref="AB54:AC58 AC59:AC63" formula="1" formulaRange="1"/>
-    <ignoredError sqref="C13:C14 E13:H13 J13:BQ13 O34:S34 L7:M7 A41:S58 A39:S39 B36:S36 E14:R14 T14:BQ14 AB34:BQ36 AB41:BQ53" formulaRange="1"/>
+    <ignoredError sqref="AB34:BQ36 O34:S34 J13:BQ13 E13:H13 C13:C14 AB54:AC58 AB41:BQ53 E14:R14 AC59:AC63" formulaRange="1"/>
+    <ignoredError sqref="B36:S36 A39:S39 A41:S58 L7:M7 E14:R14" numberStoredAsText="1" formulaRange="1"/>
+    <ignoredError sqref="AB37:BQ40 T14:BQ21 E15:R16 E15:R16 E15:R16 E14:R16 AC64:AC69 A12:H12 A13:A14 A34:M34 A70:AC70 A1:BQ1 A2:W2 Y2 A3 C3:V3 X3:Y3 A7 O7:BQ7 AB71:AC98 A99:AC99 AZ54:BQ63 AA2:BQ4 A110:AC132 AZ110:BQ132 A133:BQ159 A4:I4 A5:BQ5 A6:E6 I6:M6 I6:M6 I6:M6 I6:M6 P6:BQ6 A8:BQ8 A9:F9 A9:F9 A9:F9 A9:F9 A10:C10 A10:C10 A10:C10 A10:C10 E10:F10 E10:F10 E10:F10 E10:F10 I9:I10 I9:I10 I9:I10 I9:I10 K9:K10 K9:K10 K9:K10 K9:K10 M9:BQ10 M9:BQ10 M9:BQ10 M9:BQ10 A11:BQ11 A19:R21 E18:R18 E18:R18 E18:R18 E18:R18 A18:C18 A18:C18 A18:C18 A18:C18 A17:R17 A17:R17 A17:R17 A17:R17 A15:C16 A15:C16 A15:C16 A15:C16 A22:BQ22 A29:S33 A38:E38 G38:S38 G94:S94 B71:S72 G73:S73 F74:S93 F95:S98 K4:M4 O4:P4 I40:S40 A40:G40 R4:X4 A35:S35 A37:S37 I7:J7" numberStoredAsText="1" formula="1" formulaRange="1"/>
+    <ignoredError sqref="T41:AA58 I7:K7" numberStoredAsText="1"/>
+    <ignoredError sqref="AZ71:BQ98 AD64:AY64 Z2:Z3 A15:D16 S15:S16 A17:S21 E14:R14 A36 T40:AA40 G7:H7 K7 AD110:AY132 J4 F6:O6 A9:BQ10 T29:AA33 F38 A94:F94 A71:A72 A73:F73 A74:E93 A95:E98 N4 H40 Y4:Z4 T35:AA35" numberStoredAsText="1" formula="1"/>
+    <ignoredError sqref="AB54:AC58 AC59:AC63 AZ99:BQ99 AD54:AY63" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -22675,7 +22694,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:I135"/>
+  <dimension ref="B1:I137"/>
   <sheetFormatPr defaultColWidth="12.5833333333333" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.33333333333333" style="12" customWidth="1"/>
@@ -23973,42 +23992,42 @@
         <v>409</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>410</v>
+        <v>250</v>
       </c>
       <c r="D51" s="19">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F51" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="H51" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="H51" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="I51" s="19" t="s">
         <v>411</v>
-      </c>
-      <c r="I51" s="19" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:9">
       <c r="B52" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="C52" s="18" t="s">
         <v>413</v>
       </c>
-      <c r="C52" s="18" t="s">
-        <v>410</v>
-      </c>
       <c r="D52" s="19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G52" s="19" t="s">
         <v>284</v>
@@ -24025,19 +24044,19 @@
         <v>416</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D53" s="19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="H53" s="19" t="s">
         <v>417</v>
@@ -24051,13 +24070,13 @@
         <v>419</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D54" s="19">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F54" s="19" t="s">
         <v>278</v>
@@ -24069,33 +24088,33 @@
         <v>420</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>281</v>
+        <v>421</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:9">
       <c r="B55" s="17" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D55" s="19">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>423</v>
+        <v>281</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="2:9">
@@ -24103,51 +24122,51 @@
         <v>424</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D56" s="19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="H56" s="19" t="s">
         <v>425</v>
       </c>
       <c r="I56" s="19" t="s">
-        <v>281</v>
+        <v>426</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:9">
       <c r="B57" s="17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D57" s="19">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I57" s="19" t="s">
-        <v>428</v>
+        <v>281</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:9">
@@ -24155,51 +24174,51 @@
         <v>429</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D58" s="19">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>279</v>
+        <v>335</v>
       </c>
       <c r="H58" s="19" t="s">
         <v>430</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>281</v>
+        <v>431</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:9">
       <c r="B59" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D59" s="19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I59" s="19" t="s">
-        <v>433</v>
+        <v>281</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:9">
@@ -24207,36 +24226,36 @@
         <v>434</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D60" s="19">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="H60" s="19" t="s">
         <v>435</v>
       </c>
       <c r="I60" s="19" t="s">
-        <v>281</v>
+        <v>436</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:9">
       <c r="B61" s="17" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D61" s="19">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E61" s="19" t="s">
         <v>277</v>
@@ -24245,13 +24264,13 @@
         <v>278</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I61" s="19" t="s">
-        <v>438</v>
+        <v>281</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:9">
@@ -24259,36 +24278,36 @@
         <v>439</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D62" s="19">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F62" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="H62" s="19" t="s">
         <v>440</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>281</v>
+        <v>441</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:9">
       <c r="B63" s="17" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D63" s="19">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E63" s="19" t="s">
         <v>283</v>
@@ -24297,13 +24316,13 @@
         <v>278</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>443</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:9">
@@ -24311,13 +24330,13 @@
         <v>444</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="D64" s="19">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F64" s="19" t="s">
         <v>278</v>
@@ -24326,27 +24345,27 @@
         <v>279</v>
       </c>
       <c r="H64" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="I64" s="19" t="s">
         <v>446</v>
-      </c>
-      <c r="I64" s="19" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:9">
       <c r="B65" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="C65" s="18" t="s">
         <v>448</v>
       </c>
-      <c r="C65" s="18" t="s">
-        <v>445</v>
-      </c>
       <c r="D65" s="19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>341</v>
+        <v>277</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G65" s="19" t="s">
         <v>279</v>
@@ -24355,82 +24374,82 @@
         <v>449</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>281</v>
+        <v>450</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:9">
       <c r="B66" s="17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D66" s="19">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>277</v>
+        <v>341</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="H66" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="H66" s="19" t="s">
         <v>452</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>453</v>
+        <v>281</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:9">
       <c r="B67" s="17" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D67" s="19">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E67" s="19" t="s">
         <v>277</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="H67" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="H67" s="20" t="s">
         <v>455</v>
       </c>
       <c r="I67" s="19" t="s">
-        <v>281</v>
+        <v>456</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:9">
       <c r="B68" s="17" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D68" s="19">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E68" s="19" t="s">
         <v>277</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="H68" s="20" t="s">
-        <v>457</v>
+        <v>335</v>
+      </c>
+      <c r="H68" s="19" t="s">
+        <v>458</v>
       </c>
       <c r="I68" s="19" t="s">
         <v>281</v>
@@ -24438,13 +24457,13 @@
     </row>
     <row r="69" customHeight="1" spans="2:9">
       <c r="B69" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D69" s="19">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E69" s="19" t="s">
         <v>277</v>
@@ -24455,8 +24474,8 @@
       <c r="G69" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="H69" s="19" t="s">
-        <v>459</v>
+      <c r="H69" s="20" t="s">
+        <v>460</v>
       </c>
       <c r="I69" s="19" t="s">
         <v>281</v>
@@ -24464,25 +24483,25 @@
     </row>
     <row r="70" customHeight="1" spans="2:9">
       <c r="B70" s="17" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D70" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G70" s="19" t="s">
         <v>279</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="I70" s="19" t="s">
         <v>281</v>
@@ -24490,16 +24509,16 @@
     </row>
     <row r="71" customHeight="1" spans="2:9">
       <c r="B71" s="17" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D71" s="19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>341</v>
+        <v>283</v>
       </c>
       <c r="F71" s="19" t="s">
         <v>101</v>
@@ -24508,7 +24527,7 @@
         <v>279</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I71" s="19" t="s">
         <v>281</v>
@@ -24516,28 +24535,28 @@
     </row>
     <row r="72" customHeight="1" spans="2:9">
       <c r="B72" s="17" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D72" s="19">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>283</v>
+        <v>341</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G72" s="19" t="s">
         <v>279</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>466</v>
+        <v>281</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:9">
@@ -24545,16 +24564,16 @@
         <v>467</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D73" s="19">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>341</v>
+        <v>283</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G73" s="19" t="s">
         <v>279</v>
@@ -24563,27 +24582,27 @@
         <v>468</v>
       </c>
       <c r="I73" s="19" t="s">
-        <v>281</v>
+        <v>469</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:9">
       <c r="B74" s="17" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="D74" s="19">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>277</v>
+        <v>341</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>377</v>
+        <v>279</v>
       </c>
       <c r="H74" s="19" t="s">
         <v>471</v>
@@ -24597,10 +24616,10 @@
         <v>472</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D75" s="19">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E75" s="19" t="s">
         <v>277</v>
@@ -24609,10 +24628,10 @@
         <v>278</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>284</v>
+        <v>377</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I75" s="19" t="s">
         <v>281</v>
@@ -24620,28 +24639,28 @@
     </row>
     <row r="76" customHeight="1" spans="2:9">
       <c r="B76" s="17" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D76" s="19">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I76" s="19" t="s">
-        <v>476</v>
+        <v>281</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:9">
@@ -24649,10 +24668,10 @@
         <v>477</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D77" s="19">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>283</v>
@@ -24661,7 +24680,7 @@
         <v>101</v>
       </c>
       <c r="G77" s="19" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="H77" s="19" t="s">
         <v>478</v>
@@ -24675,51 +24694,51 @@
         <v>480</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D78" s="19">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G78" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="H78" s="19" t="s">
         <v>481</v>
       </c>
-      <c r="H78" s="19" t="s">
+      <c r="I78" s="19" t="s">
         <v>482</v>
-      </c>
-      <c r="I78" s="19" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="2:9">
       <c r="B79" s="17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D79" s="19">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F79" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G79" s="19" t="s">
+        <v>484</v>
+      </c>
+      <c r="H79" s="19" t="s">
         <v>485</v>
       </c>
-      <c r="H79" s="19" t="s">
+      <c r="I79" s="19" t="s">
         <v>486</v>
-      </c>
-      <c r="I79" s="19" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:9">
@@ -24727,22 +24746,22 @@
         <v>487</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D80" s="19">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F80" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>279</v>
+        <v>488</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I80" s="19" t="s">
         <v>281</v>
@@ -24750,13 +24769,13 @@
     </row>
     <row r="81" customHeight="1" spans="2:9">
       <c r="B81" s="17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D81" s="19">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E81" s="19" t="s">
         <v>283</v>
@@ -24765,13 +24784,13 @@
         <v>278</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>481</v>
+        <v>279</v>
       </c>
       <c r="H81" s="19" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I81" s="19" t="s">
-        <v>491</v>
+        <v>281</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:9">
@@ -24779,10 +24798,10 @@
         <v>492</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D82" s="19">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E82" s="19" t="s">
         <v>283</v>
@@ -24791,79 +24810,79 @@
         <v>278</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>279</v>
+        <v>484</v>
       </c>
       <c r="H82" s="19" t="s">
         <v>493</v>
       </c>
       <c r="I82" s="19" t="s">
-        <v>281</v>
+        <v>494</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:9">
       <c r="B83" s="17" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D83" s="19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E83" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F83" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>495</v>
+        <v>279</v>
       </c>
       <c r="H83" s="19" t="s">
         <v>496</v>
       </c>
       <c r="I83" s="19" t="s">
-        <v>497</v>
+        <v>281</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="2:9">
       <c r="B84" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="D84" s="19">
+        <v>11</v>
+      </c>
+      <c r="E84" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="F84" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="G84" s="19" t="s">
         <v>498</v>
-      </c>
-      <c r="C84" s="18" t="s">
-        <v>470</v>
-      </c>
-      <c r="D84" s="19">
-        <v>27</v>
-      </c>
-      <c r="E84" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="F84" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="G84" s="19" t="s">
-        <v>279</v>
       </c>
       <c r="H84" s="19" t="s">
         <v>499</v>
       </c>
       <c r="I84" s="19" t="s">
-        <v>281</v>
+        <v>500</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="2:9">
       <c r="B85" s="17" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="D85" s="19">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F85" s="19" t="s">
         <v>278</v>
@@ -24875,33 +24894,33 @@
         <v>502</v>
       </c>
       <c r="I85" s="19" t="s">
-        <v>503</v>
+        <v>281</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="2:9">
       <c r="B86" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="C86" s="18" t="s">
         <v>504</v>
       </c>
-      <c r="C86" s="18" t="s">
-        <v>501</v>
-      </c>
       <c r="D86" s="19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="F86" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G86" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="H86" s="19" t="s">
         <v>505</v>
       </c>
-      <c r="H86" s="19" t="s">
+      <c r="I86" s="19" t="s">
         <v>506</v>
-      </c>
-      <c r="I86" s="19" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:9">
@@ -24909,22 +24928,22 @@
         <v>507</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D87" s="19">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E87" s="19" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="F87" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>284</v>
+        <v>508</v>
       </c>
       <c r="H87" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I87" s="19" t="s">
         <v>281</v>
@@ -24932,48 +24951,48 @@
     </row>
     <row r="88" customHeight="1" spans="2:9">
       <c r="B88" s="17" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D88" s="19">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E88" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F88" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>510</v>
+        <v>284</v>
       </c>
       <c r="H88" s="19" t="s">
         <v>511</v>
       </c>
       <c r="I88" s="19" t="s">
-        <v>512</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:9">
       <c r="B89" s="17" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D89" s="19">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F89" s="19" t="s">
         <v>101</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H89" s="19" t="s">
         <v>514</v>
@@ -24987,10 +25006,10 @@
         <v>516</v>
       </c>
       <c r="C90" s="18" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D90" s="19">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E90" s="19" t="s">
         <v>283</v>
@@ -24999,50 +25018,50 @@
         <v>101</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>284</v>
+        <v>513</v>
       </c>
       <c r="H90" s="19" t="s">
         <v>517</v>
       </c>
       <c r="I90" s="19" t="s">
-        <v>300</v>
+        <v>518</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:9">
       <c r="B91" s="17" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C91" s="18" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D91" s="19">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E91" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F91" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="H91" s="20" t="s">
-        <v>519</v>
+        <v>284</v>
+      </c>
+      <c r="H91" s="19" t="s">
+        <v>520</v>
       </c>
       <c r="I91" s="19" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:9">
       <c r="B92" s="17" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D92" s="19">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E92" s="19" t="s">
         <v>283</v>
@@ -25051,10 +25070,10 @@
         <v>278</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="H92" s="19" t="s">
-        <v>521</v>
+        <v>279</v>
+      </c>
+      <c r="H92" s="20" t="s">
+        <v>522</v>
       </c>
       <c r="I92" s="19" t="s">
         <v>281</v>
@@ -25062,28 +25081,28 @@
     </row>
     <row r="93" customHeight="1" spans="2:9">
       <c r="B93" s="17" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D93" s="19">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E93" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F93" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G93" s="19" t="s">
         <v>284</v>
       </c>
       <c r="H93" s="19" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I93" s="19" t="s">
-        <v>524</v>
+        <v>281</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:9">
@@ -25091,10 +25110,10 @@
         <v>525</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D94" s="19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E94" s="19" t="s">
         <v>283</v>
@@ -25109,44 +25128,44 @@
         <v>526</v>
       </c>
       <c r="I94" s="19" t="s">
-        <v>300</v>
+        <v>527</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="2:9">
       <c r="B95" s="17" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D95" s="19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E95" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F95" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>528</v>
+        <v>284</v>
       </c>
       <c r="H95" s="19" t="s">
         <v>529</v>
       </c>
       <c r="I95" s="19" t="s">
-        <v>530</v>
+        <v>300</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="2:9">
       <c r="B96" s="17" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>532</v>
+        <v>504</v>
       </c>
       <c r="D96" s="19">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E96" s="19" t="s">
         <v>283</v>
@@ -25155,13 +25174,13 @@
         <v>278</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>377</v>
+        <v>531</v>
       </c>
       <c r="H96" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="I96" s="19" t="s">
         <v>533</v>
-      </c>
-      <c r="I96" s="19" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="2:9">
@@ -25169,36 +25188,36 @@
         <v>534</v>
       </c>
       <c r="C97" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D97" s="19">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E97" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F97" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>535</v>
+        <v>377</v>
       </c>
       <c r="H97" s="19" t="s">
         <v>536</v>
       </c>
       <c r="I97" s="19" t="s">
-        <v>537</v>
+        <v>281</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="2:9">
       <c r="B98" s="17" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C98" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D98" s="19">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E98" s="19" t="s">
         <v>283</v>
@@ -25207,7 +25226,7 @@
         <v>101</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H98" s="19" t="s">
         <v>539</v>
@@ -25221,47 +25240,47 @@
         <v>541</v>
       </c>
       <c r="C99" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D99" s="19">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E99" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F99" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H99" s="19" t="s">
         <v>542</v>
       </c>
       <c r="I99" s="19" t="s">
-        <v>281</v>
+        <v>543</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="2:9">
       <c r="B100" s="17" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D100" s="19">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>544</v>
+        <v>283</v>
       </c>
       <c r="F100" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="H100" s="20" t="s">
+        <v>538</v>
+      </c>
+      <c r="H100" s="19" t="s">
         <v>545</v>
       </c>
       <c r="I100" s="19" t="s">
@@ -25273,25 +25292,25 @@
         <v>546</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D101" s="19">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>283</v>
+        <v>547</v>
       </c>
       <c r="F101" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="H101" s="20" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I101" s="19" t="s">
-        <v>548</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="2:9">
@@ -25299,51 +25318,51 @@
         <v>549</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D102" s="19">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E102" s="19" t="s">
-        <v>341</v>
+        <v>283</v>
       </c>
       <c r="F102" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="H102" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="H102" s="20" t="s">
         <v>550</v>
       </c>
       <c r="I102" s="19" t="s">
-        <v>281</v>
+        <v>551</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="2:9">
       <c r="B103" s="17" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D103" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>283</v>
+        <v>341</v>
       </c>
       <c r="F103" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G103" s="19" t="s">
-        <v>284</v>
+        <v>454</v>
       </c>
       <c r="H103" s="19" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I103" s="19" t="s">
-        <v>553</v>
+        <v>281</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="2:9">
@@ -25351,77 +25370,77 @@
         <v>554</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D104" s="19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E104" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F104" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="H104" s="19" t="s">
         <v>555</v>
       </c>
       <c r="I104" s="19" t="s">
-        <v>281</v>
+        <v>556</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="2:9">
       <c r="B105" s="17" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D105" s="19">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F105" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>535</v>
+        <v>279</v>
       </c>
       <c r="H105" s="19" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I105" s="19" t="s">
-        <v>540</v>
+        <v>281</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="2:9">
       <c r="B106" s="17" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D106" s="19">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>544</v>
+        <v>283</v>
       </c>
       <c r="F106" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>335</v>
+        <v>538</v>
       </c>
       <c r="H106" s="19" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I106" s="19" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="2:9">
@@ -25429,25 +25448,25 @@
         <v>561</v>
       </c>
       <c r="C107" s="18" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D107" s="19">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>283</v>
+        <v>547</v>
       </c>
       <c r="F107" s="19" t="s">
         <v>101</v>
       </c>
       <c r="G107" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="H107" s="19" t="s">
         <v>562</v>
       </c>
-      <c r="H107" s="19" t="s">
+      <c r="I107" s="19" t="s">
         <v>563</v>
-      </c>
-      <c r="I107" s="19" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="2:9">
@@ -25455,244 +25474,244 @@
         <v>564</v>
       </c>
       <c r="C108" s="18" t="s">
-        <v>251</v>
+        <v>535</v>
       </c>
       <c r="D108" s="19">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F108" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="G108" s="19" t="s">
         <v>565</v>
       </c>
-      <c r="G108" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="H108" s="20" t="s">
+      <c r="H108" s="19" t="s">
         <v>566</v>
       </c>
       <c r="I108" s="19" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="2:9">
       <c r="B109" s="17" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C109" s="18" t="s">
-        <v>251</v>
+        <v>535</v>
       </c>
       <c r="D109" s="19">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F109" s="19" t="s">
         <v>101</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="H109" s="20" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I109" s="19" t="s">
-        <v>570</v>
+        <v>281</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="2:9">
       <c r="B110" s="17" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C110" s="18" t="s">
         <v>251</v>
       </c>
       <c r="D110" s="19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F110" s="19" t="s">
-        <v>278</v>
+        <v>570</v>
       </c>
       <c r="G110" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="H110" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="I110" s="19" t="s">
         <v>572</v>
-      </c>
-      <c r="H110" s="20" t="s">
-        <v>573</v>
-      </c>
-      <c r="I110" s="20" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="2:9">
       <c r="B111" s="17" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C111" s="18" t="s">
         <v>251</v>
       </c>
       <c r="D111" s="19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E111" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F111" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>576</v>
+        <v>279</v>
       </c>
       <c r="H111" s="20" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="I111" s="19" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="2:9">
       <c r="B112" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="C112" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="D112" s="19">
+        <v>11</v>
+      </c>
+      <c r="E112" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="F112" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="G112" s="19" t="s">
+        <v>577</v>
+      </c>
+      <c r="H112" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="I112" s="20" t="s">
         <v>579</v>
-      </c>
-      <c r="C112" s="18" t="s">
-        <v>580</v>
-      </c>
-      <c r="D112" s="19">
-        <v>23</v>
-      </c>
-      <c r="E112" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="F112" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="G112" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="H112" s="20" t="s">
-        <v>581</v>
-      </c>
-      <c r="I112" s="20" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="2:9">
       <c r="B113" s="17" t="s">
+        <v>580</v>
+      </c>
+      <c r="C113" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="D113" s="19">
+        <v>13</v>
+      </c>
+      <c r="E113" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="F113" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="G113" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="H113" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="I113" s="19" t="s">
         <v>583</v>
-      </c>
-      <c r="C113" s="18" t="s">
-        <v>580</v>
-      </c>
-      <c r="D113" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="E113" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="F113" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="G113" s="19" t="s">
-        <v>584</v>
-      </c>
-      <c r="H113" s="20" t="s">
-        <v>585</v>
-      </c>
-      <c r="I113" s="19" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="2:9">
       <c r="B114" s="17" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D114" s="19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F114" s="19" t="s">
         <v>101</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>588</v>
-      </c>
-      <c r="H114" s="19" t="s">
-        <v>589</v>
-      </c>
-      <c r="I114" s="19" t="s">
-        <v>590</v>
+        <v>288</v>
+      </c>
+      <c r="H114" s="20" t="s">
+        <v>586</v>
+      </c>
+      <c r="I114" s="20" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="2:9">
       <c r="B115" s="17" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>580</v>
-      </c>
-      <c r="D115" s="19">
-        <v>25</v>
+        <v>585</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>570</v>
       </c>
       <c r="E115" s="19" t="s">
         <v>277</v>
       </c>
       <c r="F115" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="H115" s="20" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="I115" s="19" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="2:9">
       <c r="B116" s="17" t="s">
+        <v>592</v>
+      </c>
+      <c r="C116" s="18" t="s">
+        <v>585</v>
+      </c>
+      <c r="D116" s="19">
+        <v>22</v>
+      </c>
+      <c r="E116" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="F116" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="G116" s="19" t="s">
+        <v>593</v>
+      </c>
+      <c r="H116" s="19" t="s">
         <v>594</v>
       </c>
-      <c r="C116" s="18" t="s">
-        <v>580</v>
-      </c>
-      <c r="D116" s="19">
-        <v>18</v>
-      </c>
-      <c r="E116" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="F116" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="G116" s="19" t="s">
+      <c r="I116" s="19" t="s">
         <v>595</v>
-      </c>
-      <c r="H116" s="20" t="s">
-        <v>596</v>
-      </c>
-      <c r="I116" s="19" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="2:9">
       <c r="B117" s="17" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D117" s="19">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E117" s="19" t="s">
         <v>277</v>
@@ -25701,65 +25720,65 @@
         <v>278</v>
       </c>
       <c r="G117" s="19" t="s">
-        <v>279</v>
+        <v>581</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="I117" s="19" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="2:9">
       <c r="B118" s="17" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C118" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D118" s="19">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E118" s="19" t="s">
         <v>277</v>
       </c>
       <c r="F118" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G118" s="19" t="s">
+        <v>600</v>
+      </c>
+      <c r="H118" s="20" t="s">
+        <v>601</v>
+      </c>
+      <c r="I118" s="19" t="s">
         <v>602</v>
-      </c>
-      <c r="H118" s="20" t="s">
-        <v>603</v>
-      </c>
-      <c r="I118" s="19" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="2:9">
       <c r="B119" s="17" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D119" s="19">
         <v>20</v>
       </c>
       <c r="E119" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F119" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>602</v>
+        <v>279</v>
       </c>
       <c r="H119" s="20" t="s">
+        <v>604</v>
+      </c>
+      <c r="I119" s="19" t="s">
         <v>605</v>
-      </c>
-      <c r="I119" s="19" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="2:9">
@@ -25767,22 +25786,22 @@
         <v>606</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D120" s="19">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E120" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F120" s="19" t="s">
         <v>101</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="H120" s="19" t="s">
         <v>607</v>
+      </c>
+      <c r="H120" s="20" t="s">
+        <v>608</v>
       </c>
       <c r="I120" s="19" t="s">
         <v>281</v>
@@ -25790,25 +25809,25 @@
     </row>
     <row r="121" customHeight="1" spans="2:9">
       <c r="B121" s="17" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D121" s="19">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E121" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F121" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>279</v>
+        <v>607</v>
       </c>
       <c r="H121" s="20" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I121" s="19" t="s">
         <v>281</v>
@@ -25816,10 +25835,10 @@
     </row>
     <row r="122" customHeight="1" spans="2:9">
       <c r="B122" s="17" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D122" s="19">
         <v>18</v>
@@ -25831,10 +25850,10 @@
         <v>101</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="H122" s="20" t="s">
-        <v>611</v>
+        <v>284</v>
+      </c>
+      <c r="H122" s="19" t="s">
+        <v>612</v>
       </c>
       <c r="I122" s="19" t="s">
         <v>281</v>
@@ -25842,25 +25861,25 @@
     </row>
     <row r="123" customHeight="1" spans="2:9">
       <c r="B123" s="17" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C123" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D123" s="19">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E123" s="19" t="s">
         <v>283</v>
       </c>
       <c r="F123" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G123" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="H123" s="19" t="s">
-        <v>613</v>
+      <c r="H123" s="20" t="s">
+        <v>614</v>
       </c>
       <c r="I123" s="19" t="s">
         <v>281</v>
@@ -25868,25 +25887,25 @@
     </row>
     <row r="124" customHeight="1" spans="2:9">
       <c r="B124" s="17" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C124" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D124" s="19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F124" s="19" t="s">
         <v>101</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="H124" s="19" t="s">
-        <v>615</v>
+        <v>279</v>
+      </c>
+      <c r="H124" s="20" t="s">
+        <v>616</v>
       </c>
       <c r="I124" s="19" t="s">
         <v>281</v>
@@ -25894,25 +25913,25 @@
     </row>
     <row r="125" customHeight="1" spans="2:9">
       <c r="B125" s="17" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D125" s="19">
         <v>24</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F125" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G125" s="19" t="s">
         <v>279</v>
       </c>
       <c r="H125" s="19" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I125" s="19" t="s">
         <v>281</v>
@@ -25920,16 +25939,16 @@
     </row>
     <row r="126" customHeight="1" spans="2:9">
       <c r="B126" s="17" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C126" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D126" s="19">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E126" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F126" s="19" t="s">
         <v>101</v>
@@ -25938,7 +25957,7 @@
         <v>335</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I126" s="19" t="s">
         <v>281</v>
@@ -25946,25 +25965,25 @@
     </row>
     <row r="127" customHeight="1" spans="2:9">
       <c r="B127" s="17" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C127" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D127" s="19">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F127" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G127" s="19" t="s">
-        <v>602</v>
+        <v>279</v>
       </c>
       <c r="H127" s="19" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I127" s="19" t="s">
         <v>281</v>
@@ -25972,28 +25991,28 @@
     </row>
     <row r="128" customHeight="1" spans="2:9">
       <c r="B128" s="17" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C128" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D128" s="19">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E128" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F128" s="19" t="s">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="G128" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="H128" s="20" t="s">
-        <v>623</v>
+        <v>335</v>
+      </c>
+      <c r="H128" s="19" t="s">
+        <v>624</v>
       </c>
       <c r="I128" s="19" t="s">
-        <v>624</v>
+        <v>281</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="2:9">
@@ -26001,7 +26020,7 @@
         <v>625</v>
       </c>
       <c r="C129" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D129" s="19">
         <v>19</v>
@@ -26013,9 +26032,9 @@
         <v>101</v>
       </c>
       <c r="G129" s="19" t="s">
-        <v>602</v>
-      </c>
-      <c r="H129" s="20" t="s">
+        <v>607</v>
+      </c>
+      <c r="H129" s="19" t="s">
         <v>626</v>
       </c>
       <c r="I129" s="19" t="s">
@@ -26027,7 +26046,7 @@
         <v>627</v>
       </c>
       <c r="C130" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D130" s="19">
         <v>24</v>
@@ -26039,13 +26058,13 @@
         <v>278</v>
       </c>
       <c r="G130" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="H130" s="20" t="s">
         <v>628</v>
       </c>
-      <c r="H130" s="20" t="s">
+      <c r="I130" s="19" t="s">
         <v>629</v>
-      </c>
-      <c r="I130" s="19" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="2:9">
@@ -26053,21 +26072,21 @@
         <v>630</v>
       </c>
       <c r="C131" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D131" s="19">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E131" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F131" s="19" t="s">
         <v>101</v>
       </c>
       <c r="G131" s="19" t="s">
-        <v>572</v>
-      </c>
-      <c r="H131" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="H131" s="20" t="s">
         <v>631</v>
       </c>
       <c r="I131" s="19" t="s">
@@ -26079,22 +26098,22 @@
         <v>632</v>
       </c>
       <c r="C132" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D132" s="19">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E132" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F132" s="19" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="G132" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="H132" s="19" t="s">
         <v>633</v>
+      </c>
+      <c r="H132" s="20" t="s">
+        <v>634</v>
       </c>
       <c r="I132" s="19" t="s">
         <v>281</v>
@@ -26102,28 +26121,28 @@
     </row>
     <row r="133" customHeight="1" spans="2:9">
       <c r="B133" s="17" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C133" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D133" s="19">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F133" s="19" t="s">
         <v>101</v>
       </c>
       <c r="G133" s="19" t="s">
-        <v>572</v>
-      </c>
-      <c r="H133" s="20" t="s">
-        <v>635</v>
+        <v>577</v>
+      </c>
+      <c r="H133" s="19" t="s">
+        <v>636</v>
       </c>
       <c r="I133" s="19" t="s">
-        <v>636</v>
+        <v>281</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="2:9">
@@ -26131,10 +26150,10 @@
         <v>637</v>
       </c>
       <c r="C134" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D134" s="19">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E134" s="19" t="s">
         <v>283</v>
@@ -26143,9 +26162,9 @@
         <v>101</v>
       </c>
       <c r="G134" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="H134" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="H134" s="19" t="s">
         <v>638</v>
       </c>
       <c r="I134" s="19" t="s">
@@ -26153,29 +26172,81 @@
       </c>
     </row>
     <row r="135" customHeight="1" spans="2:9">
-      <c r="B135" s="13" t="s">
+      <c r="B135" s="17" t="s">
         <v>639</v>
       </c>
       <c r="C135" s="18" t="s">
+        <v>585</v>
+      </c>
+      <c r="D135" s="19">
+        <v>16</v>
+      </c>
+      <c r="E135" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="F135" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="G135" s="19" t="s">
+        <v>577</v>
+      </c>
+      <c r="H135" s="20" t="s">
         <v>640</v>
       </c>
-      <c r="D135" s="19">
+      <c r="I135" s="19" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="2:9">
+      <c r="B136" s="17" t="s">
+        <v>642</v>
+      </c>
+      <c r="C136" s="18" t="s">
+        <v>585</v>
+      </c>
+      <c r="D136" s="19">
+        <v>14</v>
+      </c>
+      <c r="E136" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="F136" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="G136" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="H136" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="I136" s="19" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="2:9">
+      <c r="B137" s="13" t="s">
+        <v>644</v>
+      </c>
+      <c r="C137" s="18" t="s">
+        <v>645</v>
+      </c>
+      <c r="D137" s="19">
         <v>28</v>
       </c>
-      <c r="E135" s="19" t="s">
+      <c r="E137" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="F135" s="19" t="s">
+      <c r="F137" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="G135" s="19" t="s">
-        <v>641</v>
-      </c>
-      <c r="H135" s="20" t="s">
-        <v>642</v>
-      </c>
-      <c r="I135" s="19" t="s">
-        <v>593</v>
+      <c r="G137" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="H137" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="I137" s="19" t="s">
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -26201,30 +26272,30 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="8" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B2" s="8">
         <v>100</v>
@@ -26233,10 +26304,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="F2" s="8">
         <v>50</v>
@@ -26247,7 +26318,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="9" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="B3" s="8">
         <v>50</v>
@@ -26256,10 +26327,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="F3" s="8">
         <v>70</v>
@@ -26270,7 +26341,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="9" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B4" s="8">
         <v>120</v>
@@ -26279,10 +26350,10 @@
         <v>3</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="F4" s="8">
         <v>100</v>
@@ -26293,7 +26364,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="9" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B5" s="8">
         <v>300</v>
@@ -26302,10 +26373,10 @@
         <v>5</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F5" s="8">
         <v>120</v>
@@ -26316,7 +26387,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="9" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B6" s="8">
         <v>70</v>
@@ -26325,10 +26396,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="F6" s="8">
         <v>150</v>
@@ -26339,7 +26410,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="9" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="B7" s="8">
         <v>50</v>
@@ -26348,10 +26419,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="F7" s="8">
         <v>200</v>
@@ -26362,7 +26433,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="9" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="B8" s="8">
         <v>10</v>
@@ -26371,10 +26442,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="F8" s="8">
         <v>500</v>
@@ -26385,7 +26456,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="9" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B9" s="8">
         <v>150</v>
@@ -26394,12 +26465,12 @@
         <v>1</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="9" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
@@ -26425,7 +26496,7 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:20">
       <c r="A1" s="2" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>22</v>
@@ -26434,7 +26505,7 @@
         <v>91</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>92</v>
@@ -26443,19 +26514,19 @@
         <v>93</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>82</v>
@@ -26470,13 +26541,13 @@
         <v>85</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="S1" s="1" t="str" cm="1">
         <f t="array" ref="S1:S9">_xlfn.UNIQUE(灵能表[灵能类别])</f>
@@ -26492,7 +26563,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -26507,7 +26578,7 @@
         <v>4.5</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="H2" s="3">
         <v>0</v>
@@ -26526,22 +26597,22 @@
         <v>0</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="Q2" s="3">
         <v>-30</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="S2" s="1" t="str">
         <v>生化学科</v>
@@ -26552,7 +26623,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -26567,7 +26638,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="H3" s="3">
         <v>1</v>
@@ -26586,22 +26657,22 @@
         <v>6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="Q3" s="3">
         <v>-20</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="S3" s="1" t="str">
         <v>预言学科</v>
@@ -26612,7 +26683,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C4" s="2">
         <v>2</v>
@@ -26627,7 +26698,7 @@
         <v>18</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="H4" s="3">
         <v>2</v>
@@ -26646,22 +26717,22 @@
         <v>12</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="Q4" s="3">
         <v>-10</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="S4" s="1" t="str">
         <v>操火学科</v>
@@ -26672,7 +26743,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -26689,7 +26760,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
@@ -26708,22 +26779,22 @@
         <v>18</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="Q5" s="3">
         <v>0</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="S5" s="1" t="str">
         <v>遥感学科</v>
@@ -26734,7 +26805,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2">
         <v>4</v>
@@ -26749,7 +26820,7 @@
         <v>72</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="H6" s="3">
         <v>4</v>
@@ -26768,22 +26839,22 @@
         <v>24</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="Q6" s="3">
         <v>10</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="S6" s="1" t="str">
         <v>传心学科</v>
@@ -26794,7 +26865,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C7" s="2">
         <v>5</v>
@@ -26809,7 +26880,7 @@
         <v>108</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="H7" s="3">
         <v>5</v>
@@ -26828,22 +26899,22 @@
         <v>30</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="Q7" s="3">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="S7" s="1" t="str">
         <v>次级秘仪</v>
@@ -26854,7 +26925,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C8" s="2">
         <v>6</v>
@@ -26869,7 +26940,7 @@
         <v>144</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="H8" s="3">
         <v>6</v>
@@ -26888,22 +26959,22 @@
         <v>36</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="Q8" s="3">
         <v>30</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="S8" s="1" t="str">
         <v>高阶秘仪</v>
@@ -26914,7 +26985,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="C9" s="2">
         <v>7</v>
@@ -26929,7 +27000,7 @@
         <v>180</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="H9" s="3">
         <v>7</v>
@@ -26948,16 +27019,16 @@
         <v>42</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="S9" s="1" t="str">
         <v>其他灵能</v>
@@ -26968,7 +27039,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="C10" s="2">
         <v>8</v>
@@ -26983,7 +27054,7 @@
         <v>224</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="H10" s="3">
         <v>8</v>
@@ -27002,16 +27073,16 @@
         <v>48</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:20">
@@ -27019,7 +27090,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="C11" s="2">
         <v>9</v>
@@ -27050,16 +27121,16 @@
         <v>54</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:20">
@@ -27067,7 +27138,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="C12" s="2">
         <v>10</v>
@@ -27098,16 +27169,16 @@
         <v>60</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:20">
@@ -27115,7 +27186,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="C13" s="2">
         <v>11</v>
@@ -27130,7 +27201,7 @@
         <v>360</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:20">
@@ -27138,7 +27209,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="C14" s="2">
         <v>12</v>
@@ -27153,7 +27224,7 @@
         <v>448</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:20">
@@ -27161,7 +27232,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="C15" s="2">
         <v>13</v>
@@ -27176,7 +27247,7 @@
         <v>900</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:20">
@@ -27184,7 +27255,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="C16" s="2">
         <v>14</v>
@@ -27199,7 +27270,7 @@
         <v>1348</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:18">
@@ -27207,7 +27278,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="C17" s="2">
         <v>15</v>
@@ -27222,7 +27293,7 @@
         <v>1800</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:18">
@@ -27230,7 +27301,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="C18" s="2">
         <v>16</v>
@@ -27245,7 +27316,7 @@
         <v>2700</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:18">
@@ -27253,7 +27324,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="C19" s="2">
         <v>17</v>
@@ -27268,7 +27339,7 @@
         <v>3600</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:18">
@@ -27276,7 +27347,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="C20" s="2">
         <v>18</v>
@@ -27291,7 +27362,7 @@
         <v>5400</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:18">
@@ -27299,7 +27370,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="C21" s="2">
         <v>19</v>
@@ -27314,7 +27385,7 @@
         <v>7200</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:18">
@@ -27322,7 +27393,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="C22" s="2">
         <v>20</v>
@@ -27337,7 +27408,7 @@
         <v>9000</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:18">
@@ -27345,10 +27416,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:18">
@@ -27356,7 +27427,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:18">
@@ -27364,7 +27435,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:18">
@@ -27372,7 +27443,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:18">
@@ -27380,7 +27451,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:18">
@@ -27388,7 +27459,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:18">
@@ -27396,7 +27467,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:18">
@@ -27404,7 +27475,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:18">
@@ -27412,7 +27483,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:18">
@@ -27420,7 +27491,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:2">
@@ -27428,7 +27499,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:2">
@@ -27436,7 +27507,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:2">
@@ -27444,7 +27515,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:2">
@@ -27452,7 +27523,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:2">
@@ -27460,7 +27531,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:2">
@@ -27468,7 +27539,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:2">
@@ -27476,7 +27547,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:2">
@@ -27484,7 +27555,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" spans="1:2">
@@ -27492,7 +27563,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1" spans="1:2">
@@ -27500,7 +27571,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:2">
@@ -27508,7 +27579,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:2">
@@ -27516,7 +27587,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" spans="1:2">
@@ -27524,7 +27595,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:2">
@@ -27532,7 +27603,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" spans="1:2">
@@ -27540,7 +27611,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1" spans="1:2">
@@ -27548,7 +27619,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1" spans="1:2">
@@ -27556,7 +27627,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1" spans="1:2">
@@ -27564,7 +27635,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1" spans="1:2">
@@ -27572,7 +27643,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:2">
@@ -27580,7 +27651,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" spans="1:2">
@@ -27588,7 +27659,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" spans="1:2">
@@ -27596,7 +27667,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" spans="1:2">
@@ -27604,7 +27675,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" spans="1:2">
@@ -27612,7 +27683,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" spans="1:2">
@@ -27620,7 +27691,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" spans="1:2">
@@ -27628,7 +27699,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" spans="1:2">
@@ -27636,7 +27707,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" spans="1:2">
@@ -27644,7 +27715,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" spans="1:2">
@@ -27652,7 +27723,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1" spans="1:2">
@@ -27660,7 +27731,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1" spans="1:2">
@@ -27668,7 +27739,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1" spans="1:2">
@@ -27676,7 +27747,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1" spans="1:2">
@@ -27684,7 +27755,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1" spans="1:2">
@@ -27692,7 +27763,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1" spans="1:2">
@@ -27700,7 +27771,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1" spans="1:2">
@@ -27708,7 +27779,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" spans="1:2">
@@ -27716,7 +27787,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:2">
@@ -27724,7 +27795,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" spans="1:2">
@@ -27732,7 +27803,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" spans="1:2">
@@ -27740,7 +27811,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" spans="1:2">
@@ -27748,7 +27819,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" spans="1:2">
@@ -27756,7 +27827,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" spans="1:2">
@@ -27764,7 +27835,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" spans="1:2">
@@ -27772,7 +27843,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1" spans="1:2">
@@ -27780,7 +27851,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1" spans="1:2">
@@ -27788,7 +27859,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1" spans="1:2">
@@ -27796,7 +27867,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" spans="1:2">
@@ -27804,7 +27875,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1" spans="1:2">
@@ -27812,7 +27883,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1" spans="1:2">
@@ -27820,7 +27891,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1" spans="1:2">
@@ -27828,7 +27899,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1" spans="1:2">
@@ -27836,7 +27907,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1" spans="1:2">
@@ -27844,7 +27915,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1" spans="1:2">
@@ -27852,7 +27923,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1" spans="1:2">
@@ -27860,7 +27931,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1" spans="1:2">
@@ -27868,7 +27939,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1" spans="1:2">
@@ -27876,7 +27947,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1" spans="1:2">
@@ -27884,7 +27955,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1" spans="1:2">
@@ -27892,7 +27963,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1" spans="1:2">
@@ -27900,7 +27971,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1" spans="1:2">
@@ -27908,7 +27979,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1" spans="1:2">
@@ -27916,7 +27987,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1" spans="1:2">
@@ -27924,7 +27995,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1" spans="1:2">
@@ -27932,7 +28003,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1" spans="1:2">
@@ -27940,7 +28011,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1" spans="1:2">
@@ -27948,7 +28019,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1" spans="1:2">
@@ -27956,7 +28027,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1" spans="1:2">
@@ -27964,7 +28035,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1" spans="1:2">
@@ -27972,7 +28043,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
     </row>
   </sheetData>
